--- a/Tables/Enum.xlsx
+++ b/Tables/Enum.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dk505\UnityProject\Team963\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B78576-A519-4179-A571-1F91E9C6F47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A430142-65E5-42BB-AD22-D9BE512D7D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7275" yWindow="4515" windowWidth="28785" windowHeight="15345" xr2:uid="{6FF0D7EC-931C-49CC-BF36-828E5175AF26}"/>
+    <workbookView xWindow="16470" yWindow="3345" windowWidth="18315" windowHeight="15345" xr2:uid="{6FF0D7EC-931C-49CC-BF36-828E5175AF26}"/>
   </bookViews>
   <sheets>
-    <sheet name="Enum" sheetId="1" r:id="rId1"/>
+    <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,31 +36,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>GradeType</t>
+    <t>ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LEGENDARY</t>
-  </si>
-  <si>
-    <t>COMMON</t>
-  </si>
-  <si>
-    <t>RARE</t>
-  </si>
-  <si>
-    <t>EPIC</t>
-  </si>
-  <si>
-    <t>UNCOMMON</t>
+    <t>Currency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,8 +90,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,13 +112,34 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -129,7 +148,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -141,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,7 +533,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -524,9 +546,7 @@
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="C3" s="3"/>
       <c r="N3" s="3"/>
       <c r="T3" s="3"/>
@@ -539,9 +559,7 @@
       <c r="AB3" s="3"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="C4" s="3"/>
       <c r="N4" s="3"/>
       <c r="T4" s="3"/>
@@ -553,9 +571,7 @@
       <c r="AB4" s="3"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="C5" s="3"/>
       <c r="N5" s="3"/>
       <c r="T5" s="3"/>
@@ -567,9 +583,7 @@
       <c r="AB5" s="3"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="C6" s="3"/>
       <c r="K6" s="3"/>
       <c r="N6" s="3"/>
@@ -740,7 +754,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A6" xr:uid="{5D180AC9-E527-4E04-8630-616878909BB7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A6" xr:uid="{5D180AC9-E527-4E04-8630-616878909BB7}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
